--- a/ExcelDataTest/ToDoList.xlsx
+++ b/ExcelDataTest/ToDoList.xlsx
@@ -1,162 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Education\PlatformSale\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B177AF7-0090-4122-82F5-05F516DF3969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Todo" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesDashboard_ToDo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SalesDashboard_ToDo'!$A$3:$F$13</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
-  <si>
-    <t>MS-SQL Platform Order Database Todo</t>
-  </si>
-  <si>
-    <t>Initial checklist for using SQLAlchemy and Alembic.</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Command / Output</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Setup</t>
-  </si>
-  <si>
-    <t>ลง sqlalchemy และ alembic ใน venv</t>
-  </si>
-  <si>
-    <t>Finished</t>
-  </si>
-  <si>
-    <t>pip install sqlalchemy alembic</t>
-  </si>
-  <si>
-    <t>Database Design</t>
-  </si>
-  <si>
-    <t>สร้าง Model Database</t>
-  </si>
-  <si>
-    <t>เริ่มจาก models สำหรับ orders / order_items / platforms</t>
-  </si>
-  <si>
-    <t>ลง fastapi ใน venv</t>
-  </si>
-  <si>
-    <t>pip install fastapi uvicorn python-multipart</t>
-  </si>
-  <si>
-    <t>ลงเสร็จแล้ว</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>ทำ API รับไฟล์ Excel Raw data ของ Shopee แล้ว upload เข้า Database</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>แยก endpoint/service สำหรับ Shopee</t>
-  </si>
-  <si>
-    <t>ทำ API รับไฟล์ Excel Raw data ของ Lazada แล้ว upload เข้า Database</t>
-  </si>
-  <si>
-    <t>แยก endpoint/service สำหรับ Lazada</t>
-  </si>
-  <si>
-    <t>ทำ API รับไฟล์ Excel Raw data ของ Tiktok แล้ว upload เข้า Database</t>
-  </si>
-  <si>
-    <t>แยก endpoint/service สำหรับ Tiktok</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF44546A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF44546A"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -175,6 +89,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF111827"/>
       </patternFill>
     </fill>
   </fills>
@@ -214,20 +138,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -235,14 +168,14 @@
   <dxfs count="7">
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <color theme="1"/>
+        <sz val="14"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -268,14 +201,14 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <color theme="1"/>
+        <sz val="14"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -301,14 +234,14 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <color theme="1"/>
+        <sz val="14"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -334,14 +267,14 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <color theme="1"/>
+        <sz val="14"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -367,14 +300,14 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <color theme="1"/>
+        <sz val="14"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -400,14 +333,14 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <color theme="1"/>
+        <sz val="14"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -433,14 +366,14 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <color theme="1"/>
+        <sz val="14"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -452,27 +385,87 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DatabaseTodoTable" displayName="DatabaseTodoTable" ref="A4:F10" dataDxfId="6">
-  <autoFilter ref="A4:F10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatabaseTodoTable" displayName="DatabaseTodoTable" ref="A4:F10" headerRowCount="1" dataDxfId="6">
+  <autoFilter ref="A4:F10"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Task" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Status" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Command / Output" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="1" name="ID" dataDxfId="5"/>
+    <tableColumn id="2" name="Phase" dataDxfId="4"/>
+    <tableColumn id="3" name="Task" dataDxfId="3"/>
+    <tableColumn id="4" name="Status" dataDxfId="2"/>
+    <tableColumn id="5" name="Command / Output" dataDxfId="1"/>
+    <tableColumn id="6" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -762,166 +755,591 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="48" customWidth="1"/>
+    <col width="10" customWidth="1" style="7" min="1" max="1"/>
+    <col width="28" customWidth="1" style="7" min="2" max="2"/>
+    <col width="62" customWidth="1" style="7" min="3" max="3"/>
+    <col width="14" customWidth="1" style="7" min="4" max="4"/>
+    <col width="16" customWidth="1" style="7" min="5" max="5"/>
+    <col width="52" customWidth="1" style="7" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="1" ht="21" customHeight="1" s="7">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Sales Dashboard ToDoList</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="7">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>KPI Summary</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Total SalesValue, Total Orders, Total Quantity Sold, Average Order Value, Cancelled Orders, Returned Orders</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>ใช้ PlatformOrder และ PlatformOrderItem เป็นหลัก</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="7">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Main Filters</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>date_from/date_to, Platform, OrderStatus, SKU/SellerSku, Province</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ควรใช้ filter ร่วมกันได้ทุกกราฟ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Sales by Platform</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Platform, OrderCount, Quantity, SalesValue, % Share</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>เทียบ Shopee กับ TikTok ก่อน แล้วค่อยเพิ่ม Lazada</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Sales Trend</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Daily/Monthly SalesValue, OrderCount, Quantity</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>เริ่มจากรายวัน แล้วเพิ่ม toggle รายเดือนภายหลัง</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="7">
+      <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Top Selling Products</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SKU, Variation, ProductName, TotalQuantity, SalesValue, OrderCount</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ต้องมีทั้ง Top by Quantity และ Top by SalesValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Order Status Breakdown</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Completed, Delivered, Cancelled, Returned</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ช่วยดูสุขภาพคำสั่งซื้อของแต่ละ platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="7">
+      <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Cancellation / Return Summary</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Cancelled Order Count, Returned Order Count, Cancelled SalesValue, Returned SalesValue, Cancel/Return Rate</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>ใช้ IsCancelled, IsReturned และ OrderStatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Province Sales</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Province, OrderCount, SalesValue, Quantity</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ควร normalize ชื่อจังหวัด เช่น กรุงเทพฯ/กรุงเทพมหานคร</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Fee / Discount Summary</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Commission, Transaction, Service, Shipping, Discount, Refund, Tax</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>ใช้ PlatformOrderFee เพื่อรวม fee ข้าม platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Clean All Export</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>เลือก Platform, เลือก date range, Export Clean_ALL format</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>ต่อยอดจาก API ExportCleanAllExcel ที่มีอยู่</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="7" min="1" max="1"/>
+    <col width="21.7109375" customWidth="1" style="7" min="2" max="2"/>
+    <col width="36" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16" customWidth="1" style="7" min="4" max="4"/>
+    <col width="34" customWidth="1" style="7" min="5" max="5"/>
+    <col width="48" customWidth="1" style="7" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1" s="7">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>MS-SQL Platform Order Database Todo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Initial checklist for using SQLAlchemy and Alembic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Command / Output</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="37.5" customHeight="1" s="7">
+      <c r="A5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ลง sqlalchemy และ alembic ใน venv</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>pip install sqlalchemy alembic</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="37.5" customHeight="1" s="7">
+      <c r="A6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Database Design</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>สร้าง Model Database</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>เริ่มจาก models สำหรับ orders / order_items / platforms</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="37.5" customHeight="1" s="7">
+      <c r="A7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>ลง fastapi ใน venv</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>pip install fastapi uvicorn python-multipart</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>ลงเสร็จแล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56.25" customHeight="1" s="7">
+      <c r="A8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ทำ API รับไฟล์ Excel Raw data ของ Shopee แล้ว upload เข้า Database</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>แยก endpoint/service สำหรับ Shopee</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56.25" customHeight="1" s="7">
+      <c r="A9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ทำ API รับไฟล์ Excel Raw data ของ Lazada แล้ว upload เข้า Database</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>แยก endpoint/service สำหรับ Lazada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56.25" customHeight="1" s="7">
+      <c r="A10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6" t="s">
-        <v>25</v>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ทำ API รับไฟล์ Excel Raw data ของ Tiktok แล้ว upload เข้า Database</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>แยก endpoint/service สำหรับ Tiktok</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -931,7 +1349,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>